--- a/animation/assets/ТОВ_Сонечко_дані.xlsx
+++ b/animation/assets/ТОВ_Сонечко_дані.xlsx
@@ -548,7 +548,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="26" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Повна назва</t>
@@ -562,7 +562,7 @@
       <c r="C3" s="4" t="n"/>
       <c r="D3" s="4" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Код ЄДРПОУ</t>
@@ -576,7 +576,7 @@
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Юридична адреса</t>
@@ -590,7 +590,7 @@
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="26" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Телефон</t>
@@ -604,7 +604,7 @@
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>IBAN</t>
@@ -618,7 +618,7 @@
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" ht="26" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Платник ПДВ</t>
@@ -632,7 +632,7 @@
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="26" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Контрагент (покупець)</t>
@@ -646,7 +646,7 @@
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="26" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Підстава</t>
@@ -660,7 +660,7 @@
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="26" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Дата</t>
@@ -716,7 +716,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>1</v>
       </c>
@@ -747,7 +747,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="28" customHeight="1">
       <c r="A15" s="10" t="n">
         <v>2</v>
       </c>
@@ -778,7 +778,7 @@
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="6" t="n">
         <v>3</v>
       </c>
@@ -809,7 +809,7 @@
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="10" t="n">
         <v>4</v>
       </c>
@@ -840,7 +840,7 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="28" customHeight="1">
       <c r="A18" s="6" t="n">
         <v>5</v>
       </c>
@@ -871,7 +871,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="28" customHeight="1">
       <c r="A19" s="10" t="n">
         <v>6</v>
       </c>
@@ -902,7 +902,7 @@
         <v/>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="28" customHeight="1">
       <c r="A20" s="6" t="n">
         <v>7</v>
       </c>
@@ -933,7 +933,7 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="28" customHeight="1">
       <c r="A21" s="10" t="n">
         <v>8</v>
       </c>
@@ -964,7 +964,7 @@
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="28" customHeight="1">
       <c r="A22" s="6" t="n">
         <v>9</v>
       </c>
@@ -995,7 +995,7 @@
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="28" customHeight="1">
       <c r="A23" s="10" t="n">
         <v>10</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v/>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="28" customHeight="1">
       <c r="A24" s="6" t="n">
         <v>11</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="28" customHeight="1">
       <c r="A25" s="10" t="n">
         <v>12</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="28" customHeight="1">
       <c r="A26" s="6" t="n">
         <v>13</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="28" customHeight="1">
       <c r="A27" s="10" t="n">
         <v>14</v>
       </c>
@@ -1150,7 +1150,7 @@
         <v/>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="28" customHeight="1">
       <c r="A28" s="6" t="n">
         <v>15</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="28" customHeight="1">
       <c r="A29" s="10" t="n">
         <v>16</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="28" customHeight="1">
       <c r="A30" s="14" t="inlineStr">
         <is>
           <t>Разом</t>
